--- a/AAAGameData/DataTables/SummonChessSkillTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessSkillTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="11855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="83">
   <si>
     <t>#</t>
   </si>
@@ -107,6 +107,9 @@
     <t>HitEffectId</t>
   </si>
   <si>
+    <t>CustomData</t>
+  </si>
+  <si>
     <t>Desc</t>
   </si>
   <si>
@@ -143,7 +146,7 @@
     <t>伤害系数:（基于攻击力/法强的百分比）如1.5=150%）</t>
   </si>
   <si>
-    <t>效果命中类型：0=瞬发1=近2=投射物 3=AO4=射线</t>
+    <t>效果命中类型：0=瞬发1=近2=投射物 3=AO4=射线,5=特殊</t>
   </si>
   <si>
     <t>投射物预制体ID（AttackHitType=2时使用）</t>
@@ -200,6 +203,9 @@
     <t>受击特效资源ID</t>
   </si>
   <si>
+    <t>自定义数据（JSON格式）</t>
+  </si>
+  <si>
     <t>技能描述</t>
   </si>
   <si>
@@ -264,6 +270,9 @@
   </si>
   <si>
     <t>月华天倾</t>
+  </si>
+  <si>
+    <t>{"MagicCircleId":3006,"ProjectilePrefabId": 3007,"SpawnHeight":0.05}</t>
   </si>
   <si>
     <t>嫦娥大招：持续5s范围多段轰击</t>
@@ -1241,8 +1250,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:AB12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -1269,10 +1278,11 @@
     <col min="23" max="24" width="16" customWidth="1"/>
     <col min="25" max="25" width="20" customWidth="1"/>
     <col min="26" max="26" width="16" customWidth="1"/>
-    <col min="27" max="27" width="50" customWidth="1"/>
+    <col min="27" max="27" width="68.625" customWidth="1"/>
+    <col min="28" max="28" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1304,8 +1314,9 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:28">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1385,179 +1396,188 @@
       <c r="AA2" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="AB2" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:28">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>28</v>
-      </c>
     </row>
-    <row r="4" ht="28.8" spans="1:27">
+    <row r="4" ht="27" spans="1:28">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:27">
+    <row r="5" ht="15" customHeight="1" spans="1:28">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>11</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1605,10 +1625,10 @@
         <v>1</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="V5" s="1">
         <v>0</v>
@@ -1625,18 +1645,19 @@
       <c r="Z5" s="1">
         <v>0</v>
       </c>
-      <c r="AA5" s="1" t="s">
-        <v>61</v>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:27">
+    <row r="6" ht="15" customHeight="1" spans="1:28">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>12</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -1684,10 +1705,10 @@
         <v>1</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="V6" s="1">
         <v>20</v>
@@ -1704,18 +1725,19 @@
       <c r="Z6" s="1">
         <v>0</v>
       </c>
-      <c r="AA6" s="1" t="s">
-        <v>63</v>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:27">
+    <row r="7" ht="15" customHeight="1" spans="1:28">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>13</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -1763,10 +1785,10 @@
         <v>1</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="V7" s="1">
         <v>0</v>
@@ -1783,18 +1805,19 @@
       <c r="Z7" s="1">
         <v>0</v>
       </c>
-      <c r="AA7" s="1" t="s">
-        <v>67</v>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:27">
+    <row r="8" ht="15" customHeight="1" spans="1:28">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>14</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
@@ -1842,10 +1865,10 @@
         <v>9</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="V8" s="1">
         <v>20</v>
@@ -1862,18 +1885,19 @@
       <c r="Z8" s="1">
         <v>0</v>
       </c>
-      <c r="AA8" s="1" t="s">
-        <v>69</v>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:27">
+    <row r="9" ht="15" customHeight="1" spans="1:28">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>21</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -1921,10 +1945,10 @@
         <v>1</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="V9" s="1">
         <v>0</v>
@@ -1941,18 +1965,19 @@
       <c r="Z9" s="1">
         <v>0</v>
       </c>
-      <c r="AA9" s="1" t="s">
-        <v>72</v>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:27">
+    <row r="10" ht="15" customHeight="1" spans="1:28">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>22</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -2000,10 +2025,10 @@
         <v>1</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="V10" s="1">
         <v>15</v>
@@ -2020,18 +2045,19 @@
       <c r="Z10" s="1">
         <v>0</v>
       </c>
-      <c r="AA10" s="1" t="s">
-        <v>75</v>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:27">
+    <row r="11" ht="15" customHeight="1" spans="1:28">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>23</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -2079,10 +2105,10 @@
         <v>9</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="V11" s="1">
         <v>25</v>
@@ -2099,18 +2125,19 @@
       <c r="Z11" s="1">
         <v>0</v>
       </c>
-      <c r="AA11" s="1" t="s">
-        <v>77</v>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:27">
+    <row r="12" ht="15" customHeight="1" spans="1:28">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>24</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
@@ -2122,7 +2149,7 @@
         <v>0.6</v>
       </c>
       <c r="H12" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
@@ -2158,10 +2185,10 @@
         <v>1</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="V12" s="1">
         <v>100</v>
@@ -2170,7 +2197,7 @@
         <v>1808</v>
       </c>
       <c r="X12" s="1">
-        <v>3006</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="1">
         <v>0</v>
@@ -2179,7 +2206,10 @@
         <v>0</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SummonChessSkillTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessSkillTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -44,6 +44,9 @@
     <t>SkillType</t>
   </si>
   <si>
+    <t>TargetDeadState</t>
+  </si>
+  <si>
     <t>DamageType</t>
   </si>
   <si>
@@ -77,9 +80,6 @@
     <t>AreaRadius</t>
   </si>
   <si>
-    <t>Duration</t>
-  </si>
-  <si>
     <t>HitCount</t>
   </si>
   <si>
@@ -140,6 +140,9 @@
     <t>技能类型：1=被动 2=普攻效果 3=主动技能 4=大招</t>
   </si>
   <si>
+    <t>作用目标存活状态</t>
+  </si>
+  <si>
     <t>伤害类型：0=无伤害 1=物理 2=魔法 3=真实</t>
   </si>
   <si>
@@ -173,9 +176,6 @@
     <t>AOE半径（0=单体）</t>
   </si>
   <si>
-    <t>持续时间（引导类技能）</t>
-  </si>
-  <si>
     <t>触发次数（多段伤害）表示一次技能触发效果的次数</t>
   </si>
   <si>
@@ -272,7 +272,7 @@
     <t>月华天倾</t>
   </si>
   <si>
-    <t>{"MagicCircleId":3006,"ProjectilePrefabId": 3007,"SpawnHeight":0.05}</t>
+    <t>{"MagicCircleId":3006,"ProjectilePrefabId":3007,"SpawnHeight":0.15,"Duration":5}</t>
   </si>
   <si>
     <t>嫦娥大招：持续5s范围多段轰击</t>
@@ -1281,24 +1281,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AB16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="47" customWidth="1"/>
-    <col min="6" max="6" width="41" customWidth="1"/>
-    <col min="7" max="8" width="50" customWidth="1"/>
-    <col min="9" max="9" width="41" customWidth="1"/>
-    <col min="10" max="10" width="50" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="15" customWidth="1"/>
-    <col min="16" max="16" width="19" customWidth="1"/>
-    <col min="17" max="17" width="24" customWidth="1"/>
+    <col min="6" max="6" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="41" customWidth="1"/>
+    <col min="8" max="9" width="50" customWidth="1"/>
+    <col min="10" max="10" width="41" customWidth="1"/>
+    <col min="11" max="11" width="50" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
+    <col min="17" max="17" width="19" customWidth="1"/>
     <col min="18" max="18" width="48" customWidth="1"/>
     <col min="19" max="19" width="50" customWidth="1"/>
     <col min="20" max="20" width="24" customWidth="1"/>
@@ -1307,7 +1307,7 @@
     <col min="23" max="24" width="16" customWidth="1"/>
     <col min="25" max="25" width="20" customWidth="1"/>
     <col min="26" max="26" width="16" customWidth="1"/>
-    <col min="27" max="27" width="214.777777777778" customWidth="1"/>
+    <col min="27" max="27" width="171.625" customWidth="1"/>
     <col min="28" max="28" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1447,10 +1447,10 @@
         <v>28</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>28</v>
@@ -1459,7 +1459,7 @@
         <v>28</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>30</v>
@@ -1513,7 +1513,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:28">
+    <row r="4" ht="27" spans="1:28">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1624,10 +1624,10 @@
         <v>0</v>
       </c>
       <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
         <v>2</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
       </c>
       <c r="L5" s="1">
         <v>0</v>
@@ -1692,31 +1692,31 @@
         <v>2</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
       </c>
       <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
         <v>2</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>3002</v>
       </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
       </c>
       <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
         <v>10</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -1790,22 +1790,22 @@
         <v>0</v>
       </c>
       <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
         <v>30</v>
       </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
       <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
         <v>10</v>
       </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
       <c r="P7" s="1">
         <v>0</v>
       </c>
       <c r="Q7" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R7" s="1">
         <v>0</v>
@@ -1852,40 +1852,40 @@
         <v>4</v>
       </c>
       <c r="F8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
         <v>2.5</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>2</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>3003</v>
       </c>
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
       <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
         <v>50</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>80</v>
       </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
       <c r="N8" s="1">
         <v>0</v>
       </c>
       <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
         <v>15</v>
       </c>
-      <c r="P8" s="1">
+      <c r="Q8" s="1">
         <v>2</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>0</v>
       </c>
       <c r="R8" s="1">
         <v>1</v>
@@ -1944,10 +1944,10 @@
         <v>0</v>
       </c>
       <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
         <v>2</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -2012,31 +2012,31 @@
         <v>2</v>
       </c>
       <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
         <v>2</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>0.8</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>2</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>3004</v>
       </c>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="1">
         <v>0</v>
       </c>
       <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
         <v>10</v>
-      </c>
-      <c r="N10" s="1">
-        <v>0</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -2092,40 +2092,40 @@
         <v>3</v>
       </c>
       <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
         <v>2</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>1.2</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>2</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>3005</v>
       </c>
-      <c r="J11" s="1">
-        <v>1</v>
-      </c>
       <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
         <v>30</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="1">
         <v>40</v>
       </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
       <c r="N11" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O11" s="1">
         <v>8</v>
       </c>
       <c r="P11" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="1">
         <v>1.5</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>0</v>
       </c>
       <c r="R11" s="1">
         <v>1</v>
@@ -2172,40 +2172,40 @@
         <v>4</v>
       </c>
       <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
         <v>2</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>0.6</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>5</v>
       </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
       <c r="J12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
         <v>20</v>
       </c>
-      <c r="L12" s="1">
+      <c r="M12" s="1">
         <v>80</v>
       </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
       <c r="N12" s="1">
         <v>0</v>
       </c>
       <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
         <v>6</v>
       </c>
-      <c r="P12" s="1">
+      <c r="Q12" s="1">
         <v>4</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>5</v>
       </c>
       <c r="R12" s="1">
         <v>10</v>
@@ -2334,7 +2334,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -2343,22 +2343,22 @@
         <v>1</v>
       </c>
       <c r="I14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="1">
         <v>0</v>
       </c>
       <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
         <v>15</v>
-      </c>
-      <c r="N14" s="1">
-        <v>0</v>
       </c>
       <c r="O14" s="1">
         <v>0</v>
@@ -2414,40 +2414,40 @@
         <v>3</v>
       </c>
       <c r="F15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
         <v>2</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>3</v>
       </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
       <c r="J15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
         <v>50</v>
       </c>
-      <c r="L15" s="1">
+      <c r="M15" s="1">
         <v>30</v>
       </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
       <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
         <v>8</v>
       </c>
-      <c r="O15" s="1">
+      <c r="P15" s="1">
         <v>2.1</v>
       </c>
-      <c r="P15" s="1">
+      <c r="Q15" s="1">
         <v>4</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>0</v>
       </c>
       <c r="R15" s="1">
         <v>0</v>
@@ -2496,40 +2496,40 @@
         <v>4</v>
       </c>
       <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
         <v>2</v>
       </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
       <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
         <v>5</v>
       </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
       <c r="J16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
         <v>60</v>
       </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
       <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
         <v>12</v>
       </c>
-      <c r="O16" s="1">
+      <c r="P16" s="1">
         <v>10</v>
       </c>
-      <c r="P16" s="1">
+      <c r="Q16" s="1">
         <v>4</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>10</v>
       </c>
       <c r="R16" s="1">
         <v>0</v>

--- a/AAAGameData/DataTables/SummonChessSkillTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessSkillTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="118">
   <si>
     <t>#</t>
   </si>
@@ -284,7 +284,7 @@
     <t>邪灵被动：普攻命中30%概率对目标施加恐惧（攻击力-20%，持续2s）</t>
   </si>
   <si>
-    <t>邪灵爪击</t>
+    <t>邪灵普攻</t>
   </si>
   <si>
     <t>邪灵普攻：近战物理伤害</t>
@@ -305,7 +305,82 @@
     <t>{"MagicCircleId":3009,"SpawnHeight":0.1,"DotInterval":1,"CorrosionInterval":5,"DotDamageCoeff":0.25,"DotBaseDamage":10,"ExplosionDamageCoeff":1.2,"ExplosionBaseDamage":30}</t>
   </si>
   <si>
-    <t>邪灵技能二：锁定目标位置生成法阵；敌人首次进入立即获得2层腐蚀；法阵内持续受到魔法伤害且每停留5秒叠加1层腐蚀（离开重置）；爆炸时对范围内敌人造成大量伤害并再施加1层腐蚀</t>
+    <t>邪灵大招：锁定目标位置生成法阵；敌人首次进入立即获得2层腐蚀；法阵内持续受到魔法伤害且每停留5秒叠加1层腐蚀（离开重置）；爆炸时对范围内敌人造成大量伤害并再施加1层腐蚀</t>
+  </si>
+  <si>
+    <t>虚无之躯</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>恶魂被动：物理伤害减免30%，虚无之物难以被伤害</t>
+  </si>
+  <si>
+    <t>恶魂普攻</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>恶魂普攻：发射黑暗能量球造成法术伤害，20%概率使目标陷入恐惧</t>
+  </si>
+  <si>
+    <t>心灵扭曲</t>
+  </si>
+  <si>
+    <t>5009</t>
+  </si>
+  <si>
+    <t>恶魂技能一：诵读古老音节，对范围内敌人造成法术伤害，使其陷入混乱状态</t>
+  </si>
+  <si>
+    <t>邪念潮涌</t>
+  </si>
+  <si>
+    <t>5009,9</t>
+  </si>
+  <si>
+    <t>恶魂大招：释放压抑已久的邪念怨恨发出冲击，对前方范围内所有敌人造成法术伤害，施加混乱状态并60%概率造成恐惧</t>
+  </si>
+  <si>
+    <t>黑暗神力</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>黑暗杨戬被动：所有攻击附带腐蚀效果，多阶段Boss</t>
+  </si>
+  <si>
+    <t>黑暗戟横扫</t>
+  </si>
+  <si>
+    <t>黑暗杨戬普攻：以黑暗戟横扫，造成物理伤害</t>
+  </si>
+  <si>
+    <t>天威圣戟·黑暗</t>
+  </si>
+  <si>
+    <t>黑暗杨戬技能一：范围清盾技能</t>
+  </si>
+  <si>
+    <t>三眼天火</t>
+  </si>
+  <si>
+    <t>黑暗杨戬技能二：直线法术伤害，施加灼烧</t>
+  </si>
+  <si>
+    <t>堕落劈山</t>
+  </si>
+  <si>
+    <t>黑暗杨戬大招：真实伤害，留下黑暗裂缝</t>
+  </si>
+  <si>
+    <t>撕咬</t>
+  </si>
+  <si>
+    <t>黑暗哮天犬普攻：近战物理伤害，附带流血</t>
   </si>
 </sst>
 </file>
@@ -1280,15 +1355,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="47" customWidth="1"/>
-    <col min="6" max="6" width="15.625" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="41" customWidth="1"/>
     <col min="8" max="9" width="50" customWidth="1"/>
     <col min="10" max="10" width="41" customWidth="1"/>
@@ -1307,8 +1382,7 @@
     <col min="23" max="24" width="16" customWidth="1"/>
     <col min="25" max="25" width="20" customWidth="1"/>
     <col min="26" max="26" width="16" customWidth="1"/>
-    <col min="27" max="27" width="171.625" customWidth="1"/>
-    <col min="28" max="28" width="50" customWidth="1"/>
+    <col min="27" max="28" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
@@ -2565,6 +2639,806 @@
         <v>92</v>
       </c>
     </row>
+    <row r="17" ht="15" customHeight="1" spans="1:28">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1">
+        <v>41</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V17" s="1">
+        <v>0</v>
+      </c>
+      <c r="W17" s="1">
+        <v>1841</v>
+      </c>
+      <c r="X17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:28">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1">
+        <v>42</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2</v>
+      </c>
+      <c r="J18" s="1">
+        <v>3010</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>20</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>1</v>
+      </c>
+      <c r="S18" s="1">
+        <v>1</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V18" s="1">
+        <v>15</v>
+      </c>
+      <c r="W18" s="1">
+        <v>1842</v>
+      </c>
+      <c r="X18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:28">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I19" s="1">
+        <v>3</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1">
+        <v>40</v>
+      </c>
+      <c r="M19" s="1">
+        <v>50</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>9</v>
+      </c>
+      <c r="P19" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <v>1</v>
+      </c>
+      <c r="S19" s="1">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V19" s="1">
+        <v>0</v>
+      </c>
+      <c r="W19" s="1">
+        <v>1843</v>
+      </c>
+      <c r="X19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:28">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1">
+        <v>44</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="1">
+        <v>4</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>3</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>50</v>
+      </c>
+      <c r="M20" s="1">
+        <v>70</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1">
+        <v>15</v>
+      </c>
+      <c r="P20" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>0</v>
+      </c>
+      <c r="R20" s="1">
+        <v>1</v>
+      </c>
+      <c r="S20" s="1">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V20" s="1">
+        <v>0</v>
+      </c>
+      <c r="W20" s="1">
+        <v>1844</v>
+      </c>
+      <c r="X20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:28">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1">
+        <v>51</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V21" s="1">
+        <v>0</v>
+      </c>
+      <c r="W21" s="1">
+        <v>1845</v>
+      </c>
+      <c r="X21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:28">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1">
+        <v>52</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>15</v>
+      </c>
+      <c r="O22" s="1">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1">
+        <v>1</v>
+      </c>
+      <c r="S22" s="1">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V22" s="1">
+        <v>0</v>
+      </c>
+      <c r="W22" s="1">
+        <v>1846</v>
+      </c>
+      <c r="X22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:28">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1">
+        <v>53</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="1">
+        <v>3</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="I23" s="1">
+        <v>3</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1">
+        <v>40</v>
+      </c>
+      <c r="M23" s="1">
+        <v>50</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>8</v>
+      </c>
+      <c r="P23" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>1</v>
+      </c>
+      <c r="S23" s="1">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V23" s="1">
+        <v>0</v>
+      </c>
+      <c r="W23" s="1">
+        <v>1847</v>
+      </c>
+      <c r="X23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:28">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1">
+        <v>54</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" s="1">
+        <v>3</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I24" s="1">
+        <v>2</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1">
+        <v>40</v>
+      </c>
+      <c r="M24" s="1">
+        <v>50</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1">
+        <v>9</v>
+      </c>
+      <c r="P24" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>0</v>
+      </c>
+      <c r="R24" s="1">
+        <v>1</v>
+      </c>
+      <c r="S24" s="1">
+        <v>0</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V24" s="1">
+        <v>0</v>
+      </c>
+      <c r="W24" s="1">
+        <v>1848</v>
+      </c>
+      <c r="X24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:28">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1">
+        <v>55</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="1">
+        <v>4</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>3</v>
+      </c>
+      <c r="H25" s="1">
+        <v>2</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1">
+        <v>100</v>
+      </c>
+      <c r="M25" s="1">
+        <v>100</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1">
+        <v>15</v>
+      </c>
+      <c r="P25" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>0</v>
+      </c>
+      <c r="R25" s="1">
+        <v>1</v>
+      </c>
+      <c r="S25" s="1">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V25" s="1">
+        <v>0</v>
+      </c>
+      <c r="W25" s="1">
+        <v>1849</v>
+      </c>
+      <c r="X25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:28">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1">
+        <v>56</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <v>15</v>
+      </c>
+      <c r="O26" s="1">
+        <v>0</v>
+      </c>
+      <c r="P26" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>0</v>
+      </c>
+      <c r="R26" s="1">
+        <v>1</v>
+      </c>
+      <c r="S26" s="1">
+        <v>0</v>
+      </c>
+      <c r="T26" s="2">
+        <v>23</v>
+      </c>
+      <c r="U26" s="2">
+        <v>0</v>
+      </c>
+      <c r="V26" s="1">
+        <v>0</v>
+      </c>
+      <c r="W26" s="1">
+        <v>1850</v>
+      </c>
+      <c r="X26" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AAAGameData/DataTables/SummonChessSkillTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessSkillTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="119">
   <si>
     <t>#</t>
   </si>
@@ -302,7 +302,7 @@
     <t>腐蚀法阵</t>
   </si>
   <si>
-    <t>{"MagicCircleId":3009,"SpawnHeight":0.1,"DotInterval":1,"CorrosionInterval":5,"DotDamageCoeff":0.25,"DotBaseDamage":10,"ExplosionDamageCoeff":1.2,"ExplosionBaseDamage":30}</t>
+    <t>{"MagicCircleId":3009,"SpawnHeight":0.1,"DotInterval":1,"CorrosionInterval":5,"DotDamageCoeff":0.3,"DotBaseDamage":10,"ExplosionDamageCoeff":1.2,"ExplosionBaseDamage":30}</t>
   </si>
   <si>
     <t>邪灵大招：锁定目标位置生成法阵；敌人首次进入立即获得2层腐蚀；法阵内持续受到魔法伤害且每停留5秒叠加1层腐蚀（离开重置）；爆炸时对范围内敌人造成大量伤害并再施加1层腐蚀</t>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>撕咬</t>
+  </si>
+  <si>
+    <t>23</t>
   </si>
   <si>
     <t>黑暗哮天犬普攻：近战物理伤害，附带流血</t>
@@ -1790,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -1873,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P7" s="1">
         <v>0</v>
@@ -1944,10 +1947,10 @@
         <v>1</v>
       </c>
       <c r="L8" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M8" s="1">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="N8" s="1">
         <v>0</v>
@@ -2092,7 +2095,7 @@
         <v>2</v>
       </c>
       <c r="H10" s="1">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I10" s="1">
         <v>2</v>
@@ -2172,7 +2175,7 @@
         <v>2</v>
       </c>
       <c r="H11" s="1">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I11" s="1">
         <v>2</v>
@@ -2193,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P11" s="1">
         <v>8</v>
@@ -2252,7 +2255,7 @@
         <v>2</v>
       </c>
       <c r="H12" s="1">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I12" s="1">
         <v>5</v>
@@ -2282,7 +2285,7 @@
         <v>4</v>
       </c>
       <c r="R12" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S12" s="1">
         <v>1</v>
@@ -2411,7 +2414,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
@@ -2491,10 +2494,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="1">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I15" s="1">
         <v>3</v>
@@ -2515,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P15" s="1">
         <v>2.1</v>
@@ -3413,11 +3416,11 @@
       <c r="S26" s="1">
         <v>0</v>
       </c>
-      <c r="T26" s="2">
-        <v>23</v>
-      </c>
-      <c r="U26" s="2">
-        <v>0</v>
+      <c r="T26" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="V26" s="1">
         <v>0</v>
@@ -3436,7 +3439,7 @@
       </c>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SummonChessSkillTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessSkillTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="131">
   <si>
     <t>#</t>
   </si>
@@ -110,7 +110,10 @@
     <t>CustomData</t>
   </si>
   <si>
-    <t>Desc</t>
+    <t>EffectText</t>
+  </si>
+  <si>
+    <t>DescText</t>
   </si>
   <si>
     <t>int</t>
@@ -206,7 +209,10 @@
     <t>自定义数据（JSON格式）</t>
   </si>
   <si>
-    <t>技能描述</t>
+    <t>技能效果（如"造成200%伤害"）</t>
+  </si>
+  <si>
+    <t>技能文本描述（补充世界观，≤30字）</t>
   </si>
   <si>
     <t>日落长弓</t>
@@ -218,13 +224,19 @@
     <t>5</t>
   </si>
   <si>
-    <t>后羿被动：白天伤害+15%，射程+30%</t>
+    <t>白天伤害+15%</t>
+  </si>
+  <si>
+    <t>逐日之弓</t>
   </si>
   <si>
     <t>后羿普攻</t>
   </si>
   <si>
-    <t>后羿普攻：物理伤害</t>
+    <t>物理伤害</t>
+  </si>
+  <si>
+    <t>射出箭矢</t>
   </si>
   <si>
     <t>神力</t>
@@ -236,13 +248,19 @@
     <t>4</t>
   </si>
   <si>
-    <t>后羿技能一：普攻附带灼烧，攻击力+25%</t>
+    <t>攻击力+25%</t>
+  </si>
+  <si>
+    <t>神灵之力</t>
   </si>
   <si>
     <t>日陨</t>
   </si>
   <si>
-    <t>后羿大招：直线穿透，无衰减，+2层灼烧</t>
+    <t>穿透范围伤害</t>
+  </si>
+  <si>
+    <t>炎日坠落</t>
   </si>
   <si>
     <t>九天玄冰</t>
@@ -251,7 +269,10 @@
     <t>6</t>
   </si>
   <si>
-    <t>嫦娥被动：被攻击减速敌人，夜晚法强+40，攻击附带寒霜</t>
+    <t>法强+40</t>
+  </si>
+  <si>
+    <t>月女之力</t>
   </si>
   <si>
     <t>嫦娥普攻</t>
@@ -260,13 +281,19 @@
     <t>2</t>
   </si>
   <si>
-    <t>嫦娥普攻：魔法伤害，附带寒霜</t>
+    <t>魔法伤害</t>
+  </si>
+  <si>
+    <t>冰晶箭雨</t>
   </si>
   <si>
     <t>朔月飞轮</t>
   </si>
   <si>
-    <t>嫦娥技能一：月形冰刃往返，命中两次</t>
+    <t>多段冰刃伤害</t>
+  </si>
+  <si>
+    <t>月刃回旋</t>
   </si>
   <si>
     <t>月华天倾</t>
@@ -275,19 +302,25 @@
     <t>{"MagicCircleId":3006,"ProjectilePrefabId":3007,"SpawnHeight":0.15,"Duration":5}</t>
   </si>
   <si>
-    <t>嫦娥大招：持续5s范围多段轰击</t>
+    <t>范围多段轰击</t>
+  </si>
+  <si>
+    <t>月华倾天</t>
   </si>
   <si>
     <t>黑暗侵染</t>
   </si>
   <si>
-    <t>邪灵被动：普攻命中30%概率对目标施加恐惧（攻击力-20%，持续2s）</t>
+    <t>30%概率施加恐惧</t>
+  </si>
+  <si>
+    <t>暗影侵蚀</t>
   </si>
   <si>
     <t>邪灵普攻</t>
   </si>
   <si>
-    <t>邪灵普攻：近战物理伤害</t>
+    <t>暗影打击</t>
   </si>
   <si>
     <t>污染斩击</t>
@@ -296,7 +329,10 @@
     <t>{"IsContinuous":true,"AOEShape":"Sector","SectorAngle":150,"TickInterval":0.05,"HitPolicy":"OncePerTarget"}</t>
   </si>
   <si>
-    <t>邪灵技能一：向前方挥出巨大范围斩击，对范围内敌人造成高额伤害并施加2层腐蚀</t>
+    <t>范围斩击伤害</t>
+  </si>
+  <si>
+    <t>腐蚀之刃</t>
   </si>
   <si>
     <t>腐蚀法阵</t>
@@ -1358,7 +1394,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1386,9 +1422,10 @@
     <col min="25" max="25" width="20" customWidth="1"/>
     <col min="26" max="26" width="16" customWidth="1"/>
     <col min="27" max="28" width="50" customWidth="1"/>
+    <col min="29" max="29" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1421,8 +1458,9 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:29">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1505,185 +1543,194 @@
       <c r="AB2" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="AC2" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:29">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="AC3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>29</v>
-      </c>
     </row>
-    <row r="4" ht="27" spans="1:28">
+    <row r="4" ht="27" spans="1:29">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:28">
+    <row r="5" ht="15" customHeight="1" spans="1:29">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>11</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1731,10 +1778,10 @@
         <v>1</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="V5" s="1">
         <v>0</v>
@@ -1753,17 +1800,20 @@
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:28">
+    <row r="6" ht="15" customHeight="1" spans="1:29">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>12</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -1811,10 +1861,10 @@
         <v>1</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V6" s="1">
         <v>20</v>
@@ -1833,17 +1883,20 @@
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:28">
+    <row r="7" ht="15" customHeight="1" spans="1:29">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>13</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -1891,10 +1944,10 @@
         <v>1</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="V7" s="1">
         <v>0</v>
@@ -1913,17 +1966,20 @@
       </c>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:28">
+    <row r="8" ht="15" customHeight="1" spans="1:29">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>14</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
@@ -1971,10 +2027,10 @@
         <v>9</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V8" s="1">
         <v>20</v>
@@ -1993,17 +2049,20 @@
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:28">
+    <row r="9" ht="15" customHeight="1" spans="1:29">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>21</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -2051,10 +2110,10 @@
         <v>1</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V9" s="1">
         <v>0</v>
@@ -2073,17 +2132,20 @@
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:28">
+    <row r="10" ht="15" customHeight="1" spans="1:29">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>22</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -2131,10 +2193,10 @@
         <v>1</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V10" s="1">
         <v>15</v>
@@ -2153,17 +2215,20 @@
       </c>
       <c r="AA10" s="1"/>
       <c r="AB10" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:28">
+    <row r="11" ht="15" customHeight="1" spans="1:29">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>23</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -2211,10 +2276,10 @@
         <v>9</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V11" s="1">
         <v>25</v>
@@ -2233,17 +2298,20 @@
       </c>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:28">
+    <row r="12" ht="15" customHeight="1" spans="1:29">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>24</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
@@ -2291,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V12" s="1">
         <v>100</v>
@@ -2312,20 +2380,23 @@
         <v>0</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:28">
+    <row r="13" ht="15" customHeight="1" spans="1:29">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>31</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -2373,10 +2444,10 @@
         <v>1</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V13" s="1">
         <v>0</v>
@@ -2395,17 +2466,20 @@
       </c>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:28">
+    <row r="14" ht="15" customHeight="1" spans="1:29">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>32</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -2453,10 +2527,10 @@
         <v>1</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V14" s="1">
         <v>0</v>
@@ -2475,17 +2549,20 @@
       </c>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:28">
+    <row r="15" ht="15" customHeight="1" spans="1:29">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>33</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E15" s="1">
         <v>3</v>
@@ -2533,10 +2610,10 @@
         <v>0</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V15" s="1">
         <v>0</v>
@@ -2554,20 +2631,23 @@
         <v>0</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>89</v>
+        <v>100</v>
+      </c>
+      <c r="AC15" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:28">
+    <row r="16" ht="15" customHeight="1" spans="1:29">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>34</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E16" s="1">
         <v>4</v>
@@ -2615,10 +2695,10 @@
         <v>1</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V16" s="1">
         <v>0</v>
@@ -2636,20 +2716,21 @@
         <v>0</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>92</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="AC16" s="1"/>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:28">
+    <row r="17" ht="15" customHeight="1" spans="1:29">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>41</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -2697,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="V17" s="1">
         <v>0</v>
@@ -2719,17 +2800,18 @@
       </c>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1" t="s">
-        <v>95</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="AC17" s="1"/>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:28">
+    <row r="18" ht="15" customHeight="1" spans="1:29">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>42</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -2777,10 +2859,10 @@
         <v>1</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V18" s="1">
         <v>15</v>
@@ -2799,17 +2881,18 @@
       </c>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1" t="s">
-        <v>98</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="AC18" s="1"/>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:28">
+    <row r="19" ht="15" customHeight="1" spans="1:29">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>43</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -2857,10 +2940,10 @@
         <v>0</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V19" s="1">
         <v>0</v>
@@ -2879,17 +2962,18 @@
       </c>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1" t="s">
-        <v>101</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="AC19" s="1"/>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:28">
+    <row r="20" ht="15" customHeight="1" spans="1:29">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>44</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E20" s="1">
         <v>4</v>
@@ -2937,10 +3021,10 @@
         <v>0</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V20" s="1">
         <v>0</v>
@@ -2959,17 +3043,18 @@
       </c>
       <c r="AA20" s="1"/>
       <c r="AB20" s="1" t="s">
-        <v>104</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC20" s="1"/>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:28">
+    <row r="21" ht="15" customHeight="1" spans="1:29">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>51</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3017,10 +3102,10 @@
         <v>0</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V21" s="1">
         <v>0</v>
@@ -3039,17 +3124,18 @@
       </c>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1" t="s">
-        <v>107</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="AC21" s="1"/>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:28">
+    <row r="22" ht="15" customHeight="1" spans="1:29">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>52</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -3097,10 +3183,10 @@
         <v>0</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V22" s="1">
         <v>0</v>
@@ -3119,17 +3205,18 @@
       </c>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="AC22" s="1"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:28">
+    <row r="23" ht="15" customHeight="1" spans="1:29">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>53</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
@@ -3177,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V23" s="1">
         <v>0</v>
@@ -3199,17 +3286,18 @@
       </c>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1" t="s">
-        <v>111</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="AC23" s="1"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:28">
+    <row r="24" ht="15" customHeight="1" spans="1:29">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>54</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -3257,10 +3345,10 @@
         <v>0</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V24" s="1">
         <v>0</v>
@@ -3279,17 +3367,18 @@
       </c>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1" t="s">
-        <v>113</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="AC24" s="1"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:28">
+    <row r="25" ht="15" customHeight="1" spans="1:29">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>55</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="E25" s="1">
         <v>4</v>
@@ -3337,10 +3426,10 @@
         <v>0</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V25" s="1">
         <v>0</v>
@@ -3359,17 +3448,18 @@
       </c>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1" t="s">
-        <v>115</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="AC25" s="1"/>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:28">
+    <row r="26" ht="15" customHeight="1" spans="1:29">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>56</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -3417,10 +3507,10 @@
         <v>0</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="V26" s="1">
         <v>0</v>
@@ -3439,8 +3529,9 @@
       </c>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="AC26" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/SummonChessSkillTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessSkillTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="143">
   <si>
     <t>#</t>
   </si>
@@ -224,19 +224,19 @@
     <t>5</t>
   </si>
   <si>
-    <t>白天伤害+15%</t>
-  </si>
-  <si>
-    <t>逐日之弓</t>
+    <t>后羿手中的弓在白日时愈发强大，射程与伤害都得到加强。</t>
+  </si>
+  <si>
+    <t>射日英雄，永不落幕。</t>
   </si>
   <si>
     <t>后羿普攻</t>
   </si>
   <si>
-    <t>物理伤害</t>
-  </si>
-  <si>
-    <t>射出箭矢</t>
+    <t>后羿拉动弓弦，射出一支箭矢，对目标造成物理伤害。</t>
+  </si>
+  <si>
+    <t>弦鸣如歌，箭落如雨。</t>
   </si>
   <si>
     <t>神力</t>
@@ -248,19 +248,19 @@
     <t>4</t>
   </si>
   <si>
-    <t>攻击力+25%</t>
-  </si>
-  <si>
-    <t>神灵之力</t>
+    <t>后羿展现神力，普通攻击附带灼烧伤害，同时攻击力获得显著提升。</t>
+  </si>
+  <si>
+    <t>神灵附体，烈火焚身。</t>
   </si>
   <si>
     <t>日陨</t>
   </si>
   <si>
-    <t>穿透范围伤害</t>
-  </si>
-  <si>
-    <t>炎日坠落</t>
+    <t>后羿在短暂蓄力后，射出一往无前的一箭，对一条直线上的敌人造成穿透伤害，并对命中的目标附带两层灼烧效果。</t>
+  </si>
+  <si>
+    <t>奉天帝之命，巡猎九日。</t>
   </si>
   <si>
     <t>九天玄冰</t>
@@ -269,10 +269,10 @@
     <t>6</t>
   </si>
   <si>
-    <t>法强+40</t>
-  </si>
-  <si>
-    <t>月女之力</t>
+    <t>嫦娥身上的寒冰之力使靠近她的敌人速度大幅下降，而她的法术力量在夜间得到增强，每次攻击都会附加冻结效果。</t>
+  </si>
+  <si>
+    <t>千年孤独，化作冰封。</t>
   </si>
   <si>
     <t>嫦娥普攻</t>
@@ -281,19 +281,19 @@
     <t>2</t>
   </si>
   <si>
-    <t>魔法伤害</t>
-  </si>
-  <si>
-    <t>冰晶箭雨</t>
+    <t>嫦娥释放月光凝聚的冰晶，对目标造成魔法伤害，并使其陷入冰冻状态。</t>
+  </si>
+  <si>
+    <t>冰冷的月光，冻结一切温度。</t>
   </si>
   <si>
     <t>朔月飞轮</t>
   </si>
   <si>
-    <t>多段冰刃伤害</t>
-  </si>
-  <si>
-    <t>月刃回旋</t>
+    <t>嫦娥发射一轮月形冰刃，在击中敌人后会自动返回，往返之间对沿途的所有敌人造成冰霜伤害。</t>
+  </si>
+  <si>
+    <t>回旋的月光，切割污浊的灵魂。</t>
   </si>
   <si>
     <t>月华天倾</t>
@@ -302,25 +302,28 @@
     <t>{"MagicCircleId":3006,"ProjectilePrefabId":3007,"SpawnHeight":0.15,"Duration":5}</t>
   </si>
   <si>
-    <t>范围多段轰击</t>
-  </si>
-  <si>
-    <t>月华倾天</t>
+    <t>嫦娥在短暂吟唱后，引导纯净的月光与寒流从天而降，在目标区域持续5秒进行多段轰击，对所有敌人造成法术伤害。</t>
+  </si>
+  <si>
+    <t>月华倾人间，寒冬冻四方。</t>
   </si>
   <si>
     <t>黑暗侵染</t>
   </si>
   <si>
-    <t>30%概率施加恐惧</t>
-  </si>
-  <si>
-    <t>暗影侵蚀</t>
+    <t>邪灵的黑暗之力会侵蚀靠近它的生灵心智，有概率使其陷入恐惧状态。</t>
+  </si>
+  <si>
+    <t>你听见了吗？黑暗的声音。</t>
   </si>
   <si>
     <t>邪灵普攻</t>
   </si>
   <si>
-    <t>暗影打击</t>
+    <t>邪灵挥动利爪，对目标造成物理伤害，其黑暗之力可能使目标陷入恐惧。</t>
+  </si>
+  <si>
+    <t>把你的恐惧送给我吧。</t>
   </si>
   <si>
     <t>污染斩击</t>
@@ -329,10 +332,10 @@
     <t>{"IsContinuous":true,"AOEShape":"Sector","SectorAngle":150,"TickInterval":0.05,"HitPolicy":"OncePerTarget"}</t>
   </si>
   <si>
-    <t>范围斩击伤害</t>
-  </si>
-  <si>
-    <t>腐蚀之刃</t>
+    <t>邪灵挥舞黑暗之力进行扇形范围斩击，持续释放腐蚀伤害，污染范围内的所有敌人。</t>
+  </si>
+  <si>
+    <t>当灵魂被污染，死亡也许是最好的解脱。</t>
   </si>
   <si>
     <t>腐蚀法阵</t>
@@ -341,7 +344,10 @@
     <t>{"MagicCircleId":3009,"SpawnHeight":0.1,"DotInterval":1,"CorrosionInterval":5,"DotDamageCoeff":0.3,"DotBaseDamage":10,"ExplosionDamageCoeff":1.2,"ExplosionBaseDamage":30}</t>
   </si>
   <si>
-    <t>邪灵大招：锁定目标位置生成法阵；敌人首次进入立即获得2层腐蚀；法阵内持续受到魔法伤害且每停留5秒叠加1层腐蚀（离开重置）；爆炸时对范围内敌人造成大量伤害并再施加1层腐蚀</t>
+    <t>邪灵锚定一处位置释放腐蚀法阵，敌人进入时立即获得2层腐蚀，停留期间每5秒再增加1层，当法阵爆炸时对范围内敌人造成大量伤害。</t>
+  </si>
+  <si>
+    <t>污秽法阵起，踏入死期至。腐蚀蔓延处，永无重生日。</t>
   </si>
   <si>
     <t>虚无之躯</t>
@@ -350,7 +356,10 @@
     <t>10</t>
   </si>
   <si>
-    <t>恶魂被动：物理伤害减免30%，虚无之物难以被伤害</t>
+    <t>恶魂乃是虚无之物，具有天生的物理伤害抵抗能力，普通武器难以对其造成伤害。</t>
+  </si>
+  <si>
+    <t>你看见我了吗？</t>
   </si>
   <si>
     <t>恶魂普攻</t>
@@ -359,7 +368,10 @@
     <t>9</t>
   </si>
   <si>
-    <t>恶魂普攻：发射黑暗能量球造成法术伤害，20%概率使目标陷入恐惧</t>
+    <t>恶魂释放压抑的黑暗能量球，对目标造成法术伤害，其邪恶力量可能使目标陷入恐惧。</t>
+  </si>
+  <si>
+    <t>脑海里回荡的低语，是谁的声音？</t>
   </si>
   <si>
     <t>心灵扭曲</t>
@@ -368,7 +380,10 @@
     <t>5009</t>
   </si>
   <si>
-    <t>恶魂技能一：诵读古老音节，对范围内敌人造成法术伤害，使其陷入混乱状态</t>
+    <t>恶魂诵读古老音节，扭曲范围内敌人的心灵，使其陷入混乱状态，对所有目标造成法术伤害。</t>
+  </si>
+  <si>
+    <t>有时理智崩溃只需一瞬间，对吧。</t>
   </si>
   <si>
     <t>邪念潮涌</t>
@@ -377,7 +392,10 @@
     <t>5009,9</t>
   </si>
   <si>
-    <t>恶魂大招：释放压抑已久的邪念怨恨发出冲击，对前方范围内所有敌人造成法术伤害，施加混乱状态并60%概率造成恐惧</t>
+    <t>恶魂释放压抑已久的怨恨，掀起邪念潮涌，对前方锥形范围内所有敌人造成法术伤害，并使其陷入混乱与恐惧状态。</t>
+  </si>
+  <si>
+    <t>倾听吧，世界的尖啸。。。</t>
   </si>
   <si>
     <t>黑暗神力</t>
@@ -386,31 +404,46 @@
     <t>21</t>
   </si>
   <si>
-    <t>黑暗杨戬被动：所有攻击附带腐蚀效果，多阶段Boss</t>
+    <t>黑暗杨戬的所有攻击都被黑暗力量所侵蚀，附加黑暗腐蚀效果，能够持续削弱敌人的防御能力。</t>
+  </si>
+  <si>
+    <t>神圣已陨落，腐蚀成为唯一的力量。</t>
   </si>
   <si>
     <t>黑暗戟横扫</t>
   </si>
   <si>
-    <t>黑暗杨戬普攻：以黑暗戟横扫，造成物理伤害</t>
+    <t>黑暗杨戬手中的黑暗戟横扫而出，对范围内的敌人造成大量物理伤害。</t>
+  </si>
+  <si>
+    <t>没有什么能挡住这一戟。</t>
   </si>
   <si>
     <t>天威圣戟·黑暗</t>
   </si>
   <si>
-    <t>黑暗杨戬技能一：范围清盾技能</t>
+    <t>黑暗杨戬挥舞黑暗圣戟进行横扫，被这股黑暗之力触及的所有护盾将被瞬间破碎。</t>
+  </si>
+  <si>
+    <t>在这圣戟面前，万般防御都是虚妄。</t>
   </si>
   <si>
     <t>三眼天火</t>
   </si>
   <si>
-    <t>黑暗杨戬技能二：直线法术伤害，施加灼烧</t>
+    <t>黑暗杨戬开启第三只眼睛，释放黑暗天火，对一条直线上的敌人造成法术伤害并附加灼烧效果。</t>
+  </si>
+  <si>
+    <t>邪火灼身，永不熄灭。</t>
   </si>
   <si>
     <t>堕落劈山</t>
   </si>
   <si>
-    <t>黑暗杨戬大招：真实伤害，留下黑暗裂缝</t>
+    <t>黑暗杨戬从背后抽出黑暗劈山斧，以毁灭之力向前劈出，对前方大范围造成真实伤害，同时在地面留下黑暗裂缝，踩入其中的敌人每秒都会流失生命。</t>
+  </si>
+  <si>
+    <t>曾经的救世主，如今带来的只有毁灭和绝望。</t>
   </si>
   <si>
     <t>撕咬</t>
@@ -419,7 +452,10 @@
     <t>23</t>
   </si>
   <si>
-    <t>黑暗哮天犬普攻：近战物理伤害，附带流血</t>
+    <t>黑暗哮天犬张开血盆大口，对目标进行撕咬，造成物理伤害并附加黑暗流血效果。</t>
+  </si>
+  <si>
+    <t>獠牙撕裂血肉。</t>
   </si>
 </sst>
 </file>
@@ -1421,8 +1457,9 @@
     <col min="23" max="24" width="16" customWidth="1"/>
     <col min="25" max="25" width="20" customWidth="1"/>
     <col min="26" max="26" width="16" customWidth="1"/>
-    <col min="27" max="28" width="50" customWidth="1"/>
-    <col min="29" max="29" width="36" customWidth="1"/>
+    <col min="27" max="27" width="50" customWidth="1"/>
+    <col min="28" max="28" width="124.375" customWidth="1"/>
+    <col min="29" max="29" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -2549,10 +2586,10 @@
       </c>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="AC14" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:29">
@@ -2562,7 +2599,7 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E15" s="1">
         <v>3</v>
@@ -2631,13 +2668,13 @@
         <v>0</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:29">
@@ -2647,7 +2684,7 @@
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E16" s="1">
         <v>4</v>
@@ -2716,12 +2753,14 @@
         <v>0</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC16" s="1"/>
+        <v>105</v>
+      </c>
+      <c r="AC16" s="1" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:29">
       <c r="A17" s="1"/>
@@ -2730,7 +2769,7 @@
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -2781,7 +2820,7 @@
         <v>63</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="V17" s="1">
         <v>0</v>
@@ -2800,9 +2839,11 @@
       </c>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AC17" s="1"/>
+        <v>109</v>
+      </c>
+      <c r="AC17" s="1" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:29">
       <c r="A18" s="1"/>
@@ -2811,7 +2852,7 @@
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -2859,7 +2900,7 @@
         <v>1</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U18" s="2" t="s">
         <v>63</v>
@@ -2881,9 +2922,11 @@
       </c>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC18" s="1"/>
+        <v>113</v>
+      </c>
+      <c r="AC18" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:29">
       <c r="A19" s="1"/>
@@ -2892,7 +2935,7 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -2940,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="U19" s="2" t="s">
         <v>63</v>
@@ -2962,9 +3005,11 @@
       </c>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC19" s="1"/>
+        <v>117</v>
+      </c>
+      <c r="AC19" s="1" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:29">
       <c r="A20" s="1"/>
@@ -2973,7 +3018,7 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E20" s="1">
         <v>4</v>
@@ -3021,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="U20" s="2" t="s">
         <v>63</v>
@@ -3043,9 +3088,11 @@
       </c>
       <c r="AA20" s="1"/>
       <c r="AB20" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC20" s="1"/>
+        <v>121</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:29">
       <c r="A21" s="1"/>
@@ -3054,7 +3101,7 @@
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3102,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="U21" s="2" t="s">
         <v>63</v>
@@ -3124,9 +3171,11 @@
       </c>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC21" s="1"/>
+        <v>125</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:29">
       <c r="A22" s="1"/>
@@ -3135,7 +3184,7 @@
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -3205,9 +3254,11 @@
       </c>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC22" s="1"/>
+        <v>128</v>
+      </c>
+      <c r="AC22" s="1" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:29">
       <c r="A23" s="1"/>
@@ -3216,7 +3267,7 @@
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
@@ -3286,9 +3337,11 @@
       </c>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AC23" s="1"/>
+        <v>131</v>
+      </c>
+      <c r="AC23" s="1" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:29">
       <c r="A24" s="1"/>
@@ -3297,7 +3350,7 @@
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -3367,9 +3420,11 @@
       </c>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC24" s="1"/>
+        <v>134</v>
+      </c>
+      <c r="AC24" s="1" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:29">
       <c r="A25" s="1"/>
@@ -3378,7 +3433,7 @@
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E25" s="1">
         <v>4</v>
@@ -3448,9 +3503,11 @@
       </c>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="AC25" s="1"/>
+        <v>137</v>
+      </c>
+      <c r="AC25" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:29">
       <c r="A26" s="1"/>
@@ -3459,7 +3516,7 @@
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -3507,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="U26" s="2" t="s">
         <v>63</v>
@@ -3529,9 +3586,11 @@
       </c>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AC26" s="1"/>
+        <v>141</v>
+      </c>
+      <c r="AC26" s="1" t="s">
+        <v>142</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/SummonChessSkillTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessSkillTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -452,7 +452,7 @@
     <t>23</t>
   </si>
   <si>
-    <t>黑暗哮天犬张开血盆大口，对目标进行撕咬，造成物理伤害并附加黑暗流血效果。</t>
+    <t>黑暗哮天犬张开血盆大口，对目标进行撕咬，造成物理伤害并附加流血效果。</t>
   </si>
   <si>
     <t>獠牙撕裂血肉。</t>
@@ -468,14 +468,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -931,148 +924,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1431,7 +1424,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AC26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -1458,7 +1451,7 @@
     <col min="25" max="25" width="20" customWidth="1"/>
     <col min="26" max="26" width="16" customWidth="1"/>
     <col min="27" max="27" width="50" customWidth="1"/>
-    <col min="28" max="28" width="124.375" customWidth="1"/>
+    <col min="28" max="28" width="124.37962962963" customWidth="1"/>
     <col min="29" max="29" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1671,7 +1664,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:29">
+    <row r="4" ht="28.8" spans="1:29">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>

--- a/AAAGameData/DataTables/SummonChessSkillTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessSkillTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="147">
   <si>
     <t>#</t>
   </si>
@@ -116,6 +116,12 @@
     <t>DescText</t>
   </si>
   <si>
+    <t>Strength</t>
+  </si>
+  <si>
+    <t>MaxWaitSeconds</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -213,6 +219,12 @@
   </si>
   <si>
     <t>技能文本描述（补充世界观，≤30字）</t>
+  </si>
+  <si>
+    <t>技能强度（用于欲望值计算，数值越大越优先）</t>
+  </si>
+  <si>
+    <t>最大等待时间（秒，技能应在此时间内被释放）</t>
   </si>
   <si>
     <t>日落长弓</t>
@@ -468,7 +480,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -924,148 +943,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1423,8 +1442,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:AE26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -1450,12 +1469,11 @@
     <col min="23" max="24" width="16" customWidth="1"/>
     <col min="25" max="25" width="20" customWidth="1"/>
     <col min="26" max="26" width="16" customWidth="1"/>
-    <col min="27" max="27" width="50" customWidth="1"/>
-    <col min="28" max="28" width="124.37962962963" customWidth="1"/>
-    <col min="29" max="29" width="50" customWidth="1"/>
+    <col min="27" max="29" width="50" customWidth="1"/>
+    <col min="30" max="31" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1489,8 +1507,10 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" spans="1:31">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1576,191 +1596,209 @@
       <c r="AC2" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="AD2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="3" spans="1:29">
+    <row r="3" spans="1:31">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="J3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="T3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="W3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y3" s="1" t="s">
+      <c r="AE3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Z3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>30</v>
-      </c>
     </row>
-    <row r="4" ht="28.8" spans="1:29">
+    <row r="4" ht="27" spans="1:31">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:29">
+    <row r="5" ht="15" customHeight="1" spans="1:31">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>11</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1808,10 +1846,10 @@
         <v>1</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="V5" s="1">
         <v>0</v>
@@ -1830,20 +1868,26 @@
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:29">
+    <row r="6" ht="15" customHeight="1" spans="1:31">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>12</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -1891,10 +1935,10 @@
         <v>1</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V6" s="1">
         <v>20</v>
@@ -1913,20 +1957,26 @@
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AC6" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:29">
+    <row r="7" ht="15" customHeight="1" spans="1:31">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>13</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -1974,10 +2024,10 @@
         <v>1</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="V7" s="1">
         <v>0</v>
@@ -1996,20 +2046,26 @@
       </c>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>40</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>5</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:29">
+    <row r="8" ht="15" customHeight="1" spans="1:31">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>14</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
@@ -2057,10 +2113,10 @@
         <v>9</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V8" s="1">
         <v>20</v>
@@ -2079,20 +2135,26 @@
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>150</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>12</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:29">
+    <row r="9" ht="15" customHeight="1" spans="1:31">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>21</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -2140,10 +2202,10 @@
         <v>1</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V9" s="1">
         <v>0</v>
@@ -2162,20 +2224,26 @@
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:29">
+    <row r="10" ht="15" customHeight="1" spans="1:31">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>22</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -2223,10 +2291,10 @@
         <v>1</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V10" s="1">
         <v>15</v>
@@ -2245,20 +2313,26 @@
       </c>
       <c r="AA10" s="1"/>
       <c r="AB10" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:29">
+    <row r="11" ht="15" customHeight="1" spans="1:31">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>23</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -2306,10 +2380,10 @@
         <v>9</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V11" s="1">
         <v>25</v>
@@ -2328,20 +2402,26 @@
       </c>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>60</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>6</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:29">
+    <row r="12" ht="15" customHeight="1" spans="1:31">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>24</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
@@ -2389,10 +2469,10 @@
         <v>1</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V12" s="1">
         <v>100</v>
@@ -2410,23 +2490,29 @@
         <v>0</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AC12" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>120</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>14</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:29">
+    <row r="13" ht="15" customHeight="1" spans="1:31">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>31</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -2474,10 +2560,10 @@
         <v>1</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V13" s="1">
         <v>0</v>
@@ -2496,20 +2582,26 @@
       </c>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:29">
+    <row r="14" ht="15" customHeight="1" spans="1:31">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>32</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -2557,10 +2649,10 @@
         <v>1</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V14" s="1">
         <v>0</v>
@@ -2579,20 +2671,26 @@
       </c>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AC14" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:29">
+    <row r="15" ht="15" customHeight="1" spans="1:31">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>33</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E15" s="1">
         <v>3</v>
@@ -2640,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V15" s="1">
         <v>0</v>
@@ -2661,23 +2759,29 @@
         <v>0</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>70</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>7</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:29">
+    <row r="16" ht="15" customHeight="1" spans="1:31">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>34</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E16" s="1">
         <v>4</v>
@@ -2725,10 +2829,10 @@
         <v>1</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V16" s="1">
         <v>0</v>
@@ -2746,23 +2850,29 @@
         <v>0</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="AC16" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
+      </c>
+      <c r="AD16" s="1">
+        <v>140</v>
+      </c>
+      <c r="AE16" s="1">
+        <v>10</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:29">
+    <row r="17" ht="15" customHeight="1" spans="1:31">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>41</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -2810,10 +2920,10 @@
         <v>0</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="V17" s="1">
         <v>0</v>
@@ -2832,20 +2942,26 @@
       </c>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
+      </c>
+      <c r="AD17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:29">
+    <row r="18" ht="15" customHeight="1" spans="1:31">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>42</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -2893,10 +3009,10 @@
         <v>1</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V18" s="1">
         <v>15</v>
@@ -2915,20 +3031,26 @@
       </c>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AC18" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
+      </c>
+      <c r="AD18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:29">
+    <row r="19" ht="15" customHeight="1" spans="1:31">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>43</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -2976,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V19" s="1">
         <v>0</v>
@@ -2998,20 +3120,26 @@
       </c>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AC19" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="AD19" s="1">
+        <v>65</v>
+      </c>
+      <c r="AE19" s="1">
+        <v>6.5</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:29">
+    <row r="20" ht="15" customHeight="1" spans="1:31">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>44</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E20" s="1">
         <v>4</v>
@@ -3059,10 +3187,10 @@
         <v>0</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V20" s="1">
         <v>0</v>
@@ -3081,20 +3209,26 @@
       </c>
       <c r="AA20" s="1"/>
       <c r="AB20" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AC20" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
+      </c>
+      <c r="AD20" s="1">
+        <v>160</v>
+      </c>
+      <c r="AE20" s="1">
+        <v>15</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:29">
+    <row r="21" ht="15" customHeight="1" spans="1:31">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>51</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3142,10 +3276,10 @@
         <v>0</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V21" s="1">
         <v>0</v>
@@ -3164,20 +3298,26 @@
       </c>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
+      </c>
+      <c r="AD21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:29">
+    <row r="22" ht="15" customHeight="1" spans="1:31">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>52</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -3225,10 +3365,10 @@
         <v>0</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V22" s="1">
         <v>0</v>
@@ -3247,20 +3387,26 @@
       </c>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
+      </c>
+      <c r="AD22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:29">
+    <row r="23" ht="15" customHeight="1" spans="1:31">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>53</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
@@ -3308,10 +3454,10 @@
         <v>0</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V23" s="1">
         <v>0</v>
@@ -3330,20 +3476,26 @@
       </c>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AC23" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
+      </c>
+      <c r="AD23" s="1">
+        <v>70</v>
+      </c>
+      <c r="AE23" s="1">
+        <v>6</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:29">
+    <row r="24" ht="15" customHeight="1" spans="1:31">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>54</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -3391,10 +3543,10 @@
         <v>0</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V24" s="1">
         <v>0</v>
@@ -3413,20 +3565,26 @@
       </c>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="AC24" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
+      </c>
+      <c r="AD24" s="1">
+        <v>65</v>
+      </c>
+      <c r="AE24" s="1">
+        <v>6.5</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:29">
+    <row r="25" ht="15" customHeight="1" spans="1:31">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>55</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E25" s="1">
         <v>4</v>
@@ -3474,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V25" s="1">
         <v>0</v>
@@ -3496,20 +3654,26 @@
       </c>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AC25" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
+      </c>
+      <c r="AD25" s="1">
+        <v>170</v>
+      </c>
+      <c r="AE25" s="1">
+        <v>15</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:29">
+    <row r="26" ht="15" customHeight="1" spans="1:31">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>56</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -3557,10 +3721,10 @@
         <v>0</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="V26" s="1">
         <v>0</v>
@@ -3579,10 +3743,16 @@
       </c>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="AC26" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
+      </c>
+      <c r="AD26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SummonChessSkillTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessSkillTable.xlsx
@@ -480,14 +480,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -943,148 +936,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2006,7 +1999,7 @@
         <v>30</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O7" s="1">
         <v>8</v>
@@ -2098,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P8" s="1">
         <v>15</v>
@@ -2273,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -2362,7 +2355,7 @@
         <v>40</v>
       </c>
       <c r="N11" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O11" s="1">
         <v>7</v>
@@ -2454,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P12" s="1">
         <v>6</v>
@@ -2720,7 +2713,7 @@
         <v>30</v>
       </c>
       <c r="N15" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O15" s="1">
         <v>10</v>
@@ -2808,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="1">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N16" s="1">
         <v>0</v>
@@ -3080,7 +3073,7 @@
         <v>50</v>
       </c>
       <c r="N19" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O19" s="1">
         <v>9</v>
@@ -3433,10 +3426,10 @@
         <v>40</v>
       </c>
       <c r="M23" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N23" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O23" s="1">
         <v>8</v>
@@ -3510,7 +3503,7 @@
         <v>1.2</v>
       </c>
       <c r="I24" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J24" s="1">
         <v>0</v>
@@ -3525,7 +3518,7 @@
         <v>50</v>
       </c>
       <c r="N24" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O24" s="1">
         <v>9</v>
@@ -3599,7 +3592,7 @@
         <v>2</v>
       </c>
       <c r="I25" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J25" s="1">
         <v>0</v>
@@ -3611,7 +3604,7 @@
         <v>100</v>
       </c>
       <c r="M25" s="1">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="N25" s="1">
         <v>0</v>

--- a/AAAGameData/DataTables/SummonChessSkillTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessSkillTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1436,7 +1436,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AE26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -1689,7 +1689,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:31">
+    <row r="4" ht="28.8" spans="1:31">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
